--- a/outputs/daily/hr_rankings_2026-07-06.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-06.xlsx
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>78</v>
       </c>
       <c r="U10" t="n">
-        <v>57.8</v>
+        <v>56.2</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -6921,7 +6921,7 @@
         <v>50</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -9891,47 +9891,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>521692</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-07T02:10:00Z</t>
+          <t>2026-07-06T18:10:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -9954,62 +9954,58 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>35</v>
+        <v>42.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.9</v>
+        <v>32.7</v>
       </c>
       <c r="R35" t="n">
-        <v>27.6</v>
+        <v>47.2</v>
       </c>
       <c r="S35" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T35" t="n">
         <v>78</v>
       </c>
       <c r="U35" t="n">
-        <v>28.6</v>
+        <v>40.7</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10029,134 +10025,142 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/29, 0 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 9.2 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>42.71</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>98.6577</t>
+          <t>100.5081</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4388</t>
+          <t>0.4234</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.3017</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>69.42</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>35.76</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>89.07</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.4856</t>
+          <t>0.3471</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.1263</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="inlineStr"/>
+          <t>17.32</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10167,27 +10171,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>671218</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-07T01:45:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10197,26 +10201,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10230,26 +10234,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>52.9</v>
+        <v>35</v>
       </c>
       <c r="Q36" t="n">
-        <v>43.6</v>
+        <v>59.9</v>
       </c>
       <c r="R36" t="n">
-        <v>19.3</v>
+        <v>27.6</v>
       </c>
       <c r="S36" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U36" t="n">
-        <v>57.6</v>
+        <v>28.6</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10263,7 +10267,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10305,134 +10309,134 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 9/29, 0 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 16.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>92.01</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>103.3794</t>
+          <t>98.6577</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4583</t>
+          <t>0.4388</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1911</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.337</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>69.42</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>37.23</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>35.76</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1706</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>40.28</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.4049</t>
+          <t>0.4856</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10443,56 +10447,56 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>671218</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-06T18:10:00Z</t>
+          <t>2026-07-07T01:45:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>50.6</v>
+        <v>51.1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10506,58 +10510,62 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>41.7</v>
+        <v>52.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>41.8</v>
+        <v>43.6</v>
       </c>
       <c r="R37" t="n">
-        <v>47.2</v>
+        <v>19.3</v>
       </c>
       <c r="S37" t="n">
-        <v>86.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T37" t="n">
         <v>50</v>
       </c>
       <c r="U37" t="n">
-        <v>63.8</v>
+        <v>57.6</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10577,142 +10585,134 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 16.8 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>92.01</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>100.4854</t>
+          <t>103.3794</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>0.4583</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.1739</t>
+          <t>0.1911</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3279</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>71.47</t>
+          <t>72.67</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>37.23</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1903</t>
+          <t>0.1706</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>40.28</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t>0.4049</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>25.26</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH37" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>26.3</t>
+        </is>
+      </c>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -10723,12 +10723,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>607208</t>
+          <t>669016</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10786,11 +10786,11 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>26.7</v>
+        <v>41.7</v>
       </c>
       <c r="Q38" t="n">
         <v>41.8</v>
@@ -10799,13 +10799,13 @@
         <v>47.2</v>
       </c>
       <c r="S38" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T38" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U38" t="n">
-        <v>87</v>
+        <v>62.9</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -10887,67 +10887,67 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>40.28</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>99.2888</t>
+          <t>100.4854</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.3715</t>
+          <t>0.446</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.1739</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.2937</t>
+          <t>0.3279</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>71.48</t>
+          <t>71.47</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>37.56</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>26.74</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1903</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -11003,24 +11003,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>521692</t>
+          <t>607208</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>2026-07-06T18:10:00Z</t>
@@ -11033,17 +11033,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -11066,26 +11066,26 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>42.2</v>
+        <v>26.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>32.7</v>
+        <v>41.8</v>
       </c>
       <c r="R39" t="n">
         <v>47.2</v>
       </c>
       <c r="S39" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T39" t="n">
         <v>78</v>
       </c>
       <c r="U39" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -11137,27 +11137,27 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 9.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -11167,97 +11167,97 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>40.28</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>100.5081</t>
+          <t>99.2888</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>0.4234</t>
+          <t>0.3715</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>0.3017</t>
+          <t>0.2937</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>71.48</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>33.42</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>38.38</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>89.07</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>0.3471</t>
+          <t>0.4436</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>0.1263</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
@@ -17391,32 +17391,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>624641</t>
+          <t>676724</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Edmundo Sosa</t>
+          <t>Jared Young</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-06T18:10:00Z</t>
+          <t>2026-07-06T23:15:00Z</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -17426,17 +17426,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Reynaldo López</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>625643</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -17454,58 +17454,62 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>31</v>
+        <v>47.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>41.8</v>
+        <v>35.7</v>
       </c>
       <c r="R62" t="n">
-        <v>47.2</v>
+        <v>30.9</v>
       </c>
       <c r="S62" t="n">
-        <v>76.2</v>
+        <v>71.7</v>
       </c>
       <c r="T62" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U62" t="n">
-        <v>22.8</v>
+        <v>4.5</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17535,17 +17539,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 1 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 4.5 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
@@ -17555,112 +17559,104 @@
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>87.28</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>99.6935</t>
+          <t>101.1051</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>0.4252</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.2053</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3114</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>73.51</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>39.92</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t>0.4761</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>25.26</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH62" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>27.44</t>
+        </is>
+      </c>
+      <c r="BG62" t="inlineStr"/>
+      <c r="BH62" t="inlineStr"/>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -17671,27 +17667,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>676724</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jared Young</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-06T23:15:00Z</t>
+          <t>2026-07-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -17701,17 +17697,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Reynaldo López</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>625643</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -17734,26 +17730,26 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>47.2</v>
+        <v>20.4</v>
       </c>
       <c r="Q63" t="n">
-        <v>35.7</v>
+        <v>56.1</v>
       </c>
       <c r="R63" t="n">
-        <v>30.9</v>
+        <v>22.6</v>
       </c>
       <c r="S63" t="n">
-        <v>71.7</v>
+        <v>95.5</v>
       </c>
       <c r="T63" t="n">
         <v>80</v>
       </c>
       <c r="U63" t="n">
-        <v>4.5</v>
+        <v>41.2</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -17767,7 +17763,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -17809,27 +17805,27 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 4.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
@@ -17839,104 +17835,104 @@
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>32.91</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>87.66</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>101.1051</t>
+          <t>97.821</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.4252</t>
+          <t>0.3348</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.2053</t>
+          <t>0.1147</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.3114</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>73.51</t>
+          <t>71.67</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>32.73</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.0862</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>41.04</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>89.89</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.4761</t>
+          <t>0.4632</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.2044</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>27.44</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr"/>
       <c r="BH63" t="inlineStr"/>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -17947,56 +17943,56 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>624641</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Edmundo Sosa</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-07T01:40:00Z</t>
+          <t>2026-07-06T18:10:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18010,62 +18006,58 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>20.4</v>
+        <v>31</v>
       </c>
       <c r="Q64" t="n">
-        <v>56.1</v>
+        <v>41.8</v>
       </c>
       <c r="R64" t="n">
-        <v>22.6</v>
+        <v>47.2</v>
       </c>
       <c r="S64" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T64" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U64" t="n">
-        <v>41.2</v>
+        <v>21.8</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18085,12 +18077,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -18100,12 +18092,12 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Last 7 games: 3/21, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
@@ -18115,104 +18107,112 @@
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>87.28</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>97.821</t>
+          <t>99.6935</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.3348</t>
+          <t>0.447</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.1147</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>71.67</t>
+          <t>72.16</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>39.63</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.0862</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>38.38</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>89.89</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.4632</t>
+          <t>0.4436</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.2044</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>21.59</t>
-        </is>
-      </c>
-      <c r="BG64" t="inlineStr"/>
-      <c r="BH64" t="inlineStr"/>
+          <t>25.26</t>
+        </is>
+      </c>
+      <c r="BG64" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH64" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>656537</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Derek Hill</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -22154,11 +22154,11 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>38</v>
+        <v>31.4</v>
       </c>
       <c r="Q79" t="n">
         <v>41.8</v>
@@ -22167,13 +22167,13 @@
         <v>47.2</v>
       </c>
       <c r="S79" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T79" t="n">
         <v>78</v>
       </c>
       <c r="U79" t="n">
-        <v>12</v>
+        <v>32.9</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -22225,22 +22225,22 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/10, 0 HR</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
@@ -22255,67 +22255,67 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>100.2609</t>
+          <t>99.4091</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.3866</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.1584</t>
+          <t>0.1447</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>72.08</t>
+          <t>72.77</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>37.66</t>
+          <t>39.99</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>28.18</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.1575</t>
+          <t>0.1291</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
@@ -22371,47 +22371,47 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>802139</t>
+          <t>656537</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JJ Wetherholt</t>
+          <t>Derek Hill</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-06T23:45:00Z</t>
+          <t>2026-07-06T18:10:00Z</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -22420,7 +22420,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -22434,65 +22434,61 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>39.1</v>
+        <v>38</v>
       </c>
       <c r="Q80" t="n">
-        <v>32</v>
+        <v>41.8</v>
       </c>
       <c r="R80" t="n">
-        <v>22.1</v>
+        <v>47.2</v>
       </c>
       <c r="S80" t="n">
-        <v>88.7</v>
+        <v>44.8</v>
       </c>
       <c r="T80" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U80" t="n">
-        <v>52.1</v>
+        <v>12</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr"/>
@@ -22509,27 +22505,27 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 2/10, 0 HR</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
@@ -22539,104 +22535,112 @@
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>99.4588</t>
+          <t>100.2609</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>0.3866</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.08</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>37.66</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.1575</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>38.38</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.4436</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="BG80" t="inlineStr"/>
-      <c r="BH80" t="inlineStr"/>
+          <t>25.26</t>
+        </is>
+      </c>
+      <c r="BG80" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr"/>
@@ -22647,27 +22651,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>802139</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>JJ Wetherholt</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-07T02:10:00Z</t>
+          <t>2026-07-06T23:45:00Z</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -22677,17 +22681,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -22710,26 +22714,26 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>29.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q81" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="R81" t="n">
-        <v>27.6</v>
+        <v>22.1</v>
       </c>
       <c r="S81" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T81" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U81" t="n">
-        <v>45.3</v>
+        <v>52.1</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -22743,7 +22747,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -22768,7 +22772,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr"/>
@@ -22785,12 +22789,12 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -22800,12 +22804,12 @@
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 1 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
@@ -22815,104 +22819,104 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>100.2456</t>
+          <t>99.4588</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>0.4292</t>
+          <t>0.442</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>0.1293</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>0.3588</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>70.55</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>0.4856</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr"/>
       <c r="BH81" t="inlineStr"/>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr"/>
@@ -22923,32 +22927,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-06T18:10:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -22958,12 +22962,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -22972,7 +22976,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -22986,58 +22990,62 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>31.4</v>
+        <v>29.2</v>
       </c>
       <c r="Q82" t="n">
-        <v>41.8</v>
+        <v>58</v>
       </c>
       <c r="R82" t="n">
-        <v>47.2</v>
+        <v>27.6</v>
       </c>
       <c r="S82" t="n">
-        <v>52.4</v>
+        <v>47.9</v>
       </c>
       <c r="T82" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U82" t="n">
-        <v>27.6</v>
+        <v>45.3</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC82" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23057,12 +23065,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -23072,12 +23080,12 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Last 7 games: 6/20, 1 HR</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
@@ -23087,112 +23095,104 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>39.62</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>89.77</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>99.4091</t>
+          <t>100.2456</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.4292</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>0.1447</t>
+          <t>0.1293</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3588</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>72.77</t>
+          <t>70.55</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>28.18</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.1291</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t>0.4856</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>25.26</t>
-        </is>
-      </c>
-      <c r="BG82" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH82" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr"/>
       <c r="BI82" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ82" t="inlineStr"/>
@@ -25159,47 +25159,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>678662</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-07T02:10:00Z</t>
+          <t>2026-07-06T18:10:00Z</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Eric Lauer</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>641778</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -25208,7 +25208,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -25222,62 +25222,58 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>29.8</v>
+        <v>27.2</v>
       </c>
       <c r="Q90" t="n">
-        <v>55.8</v>
+        <v>41.8</v>
       </c>
       <c r="R90" t="n">
-        <v>27.6</v>
+        <v>47.2</v>
       </c>
       <c r="S90" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T90" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U90" t="n">
-        <v>30.3</v>
+        <v>39.7</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25297,134 +25293,142 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 1 HR</t>
+          <t>Contact streak: 10/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 16.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>98.8959</t>
+          <t>98.6212</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.3878</t>
+          <t>0.4028</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.1569</t>
+          <t>0.1453</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.2868</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>71.81</t>
+          <t>69.75</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>35.36</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.1323</t>
+          <t>0.1452</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>38.38</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>0.4436</t>
         </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
-          <t>0.2077</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>38.09</t>
-        </is>
-      </c>
-      <c r="BG90" t="inlineStr"/>
-      <c r="BH90" t="inlineStr"/>
+          <t>25.26</t>
+        </is>
+      </c>
+      <c r="BG90" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25435,47 +25439,47 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>678662</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-06T18:10:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Eric Lauer</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>641778</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -25484,7 +25488,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25498,58 +25502,62 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>27.2</v>
+        <v>29.8</v>
       </c>
       <c r="Q91" t="n">
-        <v>41.8</v>
+        <v>55.8</v>
       </c>
       <c r="R91" t="n">
-        <v>47.2</v>
+        <v>27.6</v>
       </c>
       <c r="S91" t="n">
-        <v>64.3</v>
+        <v>40.2</v>
       </c>
       <c r="T91" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U91" t="n">
-        <v>36</v>
+        <v>30.3</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC91" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25569,142 +25577,134 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 4/20, 1 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>36.01</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>98.6212</t>
+          <t>98.8959</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.4028</t>
+          <t>0.3878</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.1453</t>
+          <t>0.1569</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.2868</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>69.75</t>
+          <t>71.81</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.1452</t>
+          <t>0.1323</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>37.77</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t>0.461</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.2077</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>25.26</t>
-        </is>
-      </c>
-      <c r="BG91" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH91" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>38.09</t>
+        </is>
+      </c>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
       <c r="BI91" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ91" t="inlineStr"/>
@@ -40774,7 +40774,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>78</v>
       </c>
       <c r="U10" t="n">
-        <v>57.8</v>
+        <v>56.2</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-07-06.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-06.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>94.7</v>
+        <v>99.5</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5771,47 +5771,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-06T22:45:00Z</t>
+          <t>2026-07-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Miles Mikolas</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>571945</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5838,22 +5838,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>44.4</v>
+        <v>50.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>57.9</v>
+        <v>56.1</v>
       </c>
       <c r="R20" t="n">
-        <v>61.2</v>
+        <v>46.1</v>
       </c>
       <c r="S20" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>44.8</v>
+        <v>62.2</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5925,122 +5925,122 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 21.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>52.57</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>92.25</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.7846</t>
+          <t>104.1997</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4495</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1764</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3056</t>
+          <t>0.3574</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>75.19</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>41.04</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>89.89</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4899</t>
+          <t>0.4632</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.2172</t>
+          <t>0.2044</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -6051,27 +6051,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-07T01:40:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6081,22 +6081,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -6114,26 +6114,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>50.2</v>
+        <v>45.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>56.1</v>
+        <v>59.9</v>
       </c>
       <c r="R21" t="n">
-        <v>46.1</v>
+        <v>62.6</v>
       </c>
       <c r="S21" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T21" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>62.2</v>
+        <v>19.9</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6185,142 +6185,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/23, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>52.57</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>92.25</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>104.1997</t>
+          <t>101.01</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4495</t>
+          <t>0.4361</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.1871</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3574</t>
+          <t>0.3286</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>75.19</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>33.94</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1248</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.89</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4632</t>
+          <t>0.4856</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.2044</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6331,27 +6331,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-07T02:10:00Z</t>
+          <t>2026-07-06T23:45:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6394,26 +6394,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>45.8</v>
+        <v>60.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>59.9</v>
+        <v>32</v>
       </c>
       <c r="R22" t="n">
-        <v>62.6</v>
+        <v>41.1</v>
       </c>
       <c r="S22" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>78</v>
       </c>
       <c r="U22" t="n">
-        <v>19.9</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -6448,7 +6448,7 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr"/>
@@ -6465,142 +6465,142 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>13.21</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>93.42</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>101.01</t>
+          <t>105.0535</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4361</t>
+          <t>0.4652</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1871</t>
+          <t>0.2061</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3286</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>25.12</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>33.94</t>
+          <t>37.54</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1932</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.4856</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6611,56 +6611,56 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-06T23:45:00Z</t>
+          <t>2026-07-06T22:40:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>57.5</v>
+        <v>57.3</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6678,22 +6678,22 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>60.1</v>
+        <v>50.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>49.4</v>
       </c>
       <c r="R23" t="n">
         <v>41.1</v>
       </c>
       <c r="S23" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T23" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U23" t="n">
-        <v>66.40000000000001</v>
+        <v>46</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -6728,7 +6728,7 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -6750,137 +6750,137 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/23, 1 HR</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>13.21</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>46.33</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>93.42</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>105.0535</t>
+          <t>100.9153</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.4652</t>
+          <t>0.463</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.2061</t>
+          <t>0.2115</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3581</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>70.23</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>37.54</t>
+          <t>43.81</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.1932</t>
+          <t>0.1982</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>42.21</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.99</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.4458</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6891,32 +6891,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-06T22:40:00Z</t>
+          <t>2026-07-06T23:15:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -6958,13 +6958,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>50.7</v>
+        <v>54.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>49.4</v>
+        <v>30.2</v>
       </c>
       <c r="R24" t="n">
-        <v>41.1</v>
+        <v>57.4</v>
       </c>
       <c r="S24" t="n">
         <v>93.2</v>
@@ -6973,7 +6973,7 @@
         <v>80</v>
       </c>
       <c r="U24" t="n">
-        <v>46</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -7025,27 +7025,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 15.4 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7055,112 +7055,112 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>100.9153</t>
+          <t>103.9802</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>0.5024</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.2115</t>
+          <t>0.2082</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.3581</t>
+          <t>0.3563</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>46.37</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.1982</t>
+          <t>0.1901</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.4458</t>
+          <t>0.3617</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -7171,12 +7171,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>686948</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>54.1</v>
+        <v>58.9</v>
       </c>
       <c r="Q25" t="n">
         <v>30.2</v>
@@ -7247,13 +7247,13 @@
         <v>57.4</v>
       </c>
       <c r="S25" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T25" t="n">
         <v>80</v>
       </c>
       <c r="U25" t="n">
-        <v>66.90000000000001</v>
+        <v>27.1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/28, 1 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -7335,67 +7335,67 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>48.76</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>103.9802</t>
+          <t>102.4409</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.5024</t>
+          <t>0.501</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.2082</t>
+          <t>0.2304</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.3563</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>75.09</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.1901</t>
+          <t>0.1985</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -7451,27 +7451,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>686948</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-06T23:15:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7486,17 +7486,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -7514,26 +7514,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>58.9</v>
+        <v>35</v>
       </c>
       <c r="Q26" t="n">
-        <v>30.2</v>
+        <v>59.9</v>
       </c>
       <c r="R26" t="n">
-        <v>57.4</v>
+        <v>62.6</v>
       </c>
       <c r="S26" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U26" t="n">
-        <v>27.1</v>
+        <v>28.6</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7585,142 +7585,142 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 1 HR</t>
+          <t>Last 7 games: 9/29, 0 HR</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 15.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>48.76</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>102.4409</t>
+          <t>98.6577</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.501</t>
+          <t>0.4388</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.2304</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.337</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>75.09</t>
+          <t>69.42</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>35.76</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1985</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.3617</t>
+          <t>0.4856</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7731,27 +7731,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>682998</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-07T02:10:00Z</t>
+          <t>2026-07-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7761,26 +7761,26 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>57.1</v>
+        <v>56.8</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7794,50 +7794,42 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>35</v>
+        <v>56.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>59.9</v>
+        <v>44.2</v>
       </c>
       <c r="R27" t="n">
-        <v>62.6</v>
+        <v>46.1</v>
       </c>
       <c r="S27" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U27" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -7845,7 +7837,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7865,12 +7861,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -7880,127 +7876,127 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/29, 0 HR</t>
+          <t>Last 7 games: 2/25, 0 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>48.08</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>98.6577</t>
+          <t>102.5754</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4388</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.2194</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.3587</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>69.42</t>
+          <t>75.26</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>55.68</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>45.69</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>35.76</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.2526</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>40.53</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.4856</t>
+          <t>0.4248</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -8011,47 +8007,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>682998</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-07T01:40:00Z</t>
+          <t>2026-07-06T22:45:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Miles Mikolas</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>571945</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8060,7 +8056,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8074,54 +8070,58 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>56.3</v>
+        <v>44.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>44.2</v>
+        <v>57.9</v>
       </c>
       <c r="R28" t="n">
-        <v>46.1</v>
+        <v>61.2</v>
       </c>
       <c r="S28" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8141,27 +8141,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/25, 0 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 12.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.1% barrel, 21.3 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8171,112 +8171,112 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>48.08</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>90.13</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>102.5754</t>
+          <t>101.7846</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.4042</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.2194</t>
+          <t>0.1764</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.3587</t>
+          <t>0.3056</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>75.26</t>
+          <t>74.17</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>55.68</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>43.74</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.2526</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>40.53</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.4248</t>
+          <t>0.4899</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.2172</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr"/>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>55.5</v>
+        <v>55.7</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>53.3</v>
+        <v>57.8</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>50</v>
       </c>
       <c r="U48" t="n">
-        <v>26.4</v>
+        <v>30</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -20904,7 +20904,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -21184,7 +21184,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -22304,7 +22304,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -23984,7 +23984,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -25660,7 +25660,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -26220,7 +26220,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -27056,7 +27056,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -28456,7 +28456,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -31804,7 +31804,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -33459,47 +33459,47 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>686452</t>
+          <t>805347</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Drew Millas</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-06T22:45:00Z</t>
+          <t>2026-07-06T23:15:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mike Burrows</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>681347</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -33508,7 +33508,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -33526,22 +33526,22 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.1</v>
+        <v>15</v>
       </c>
       <c r="Q119" t="n">
-        <v>43.7</v>
+        <v>30.2</v>
       </c>
       <c r="R119" t="n">
-        <v>61.2</v>
+        <v>57.4</v>
       </c>
       <c r="S119" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T119" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U119" t="n">
-        <v>16.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -33576,7 +33576,7 @@
       <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -33588,17 +33588,17 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -33608,12 +33608,12 @@
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 0 HR</t>
+          <t>Last 4 games: 2/11, 0 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.1% barrel, 17.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 15.4 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
@@ -33623,112 +33623,112 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>94.7821</t>
+          <t>97.3227</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.3044</t>
+          <t>0.239</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.0786</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.2784</t>
+          <t>0.197</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>67.68</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.0989</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>0.4292</t>
+          <t>0.3617</t>
         </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
-          <t>0.1738</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>27.68</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -33739,27 +33739,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>805347</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-06T23:15:00Z</t>
+          <t>2026-07-06T23:45:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -33774,12 +33774,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -33788,7 +33788,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -33806,13 +33806,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>15</v>
+        <v>11.2</v>
       </c>
       <c r="Q120" t="n">
-        <v>30.2</v>
+        <v>42.9</v>
       </c>
       <c r="R120" t="n">
-        <v>57.4</v>
+        <v>41.1</v>
       </c>
       <c r="S120" t="n">
         <v>44.8</v>
@@ -33821,7 +33821,7 @@
         <v>80</v>
       </c>
       <c r="U120" t="n">
-        <v>9.300000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
       <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr"/>
@@ -33868,17 +33868,17 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -33888,12 +33888,12 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 4 games: 2/11, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 15.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -33903,112 +33903,112 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>97.3227</t>
+          <t>96.8572</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.3008</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>69.94</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>34.06</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1028</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>0.3617</t>
+          <t>0.4006</t>
         </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1525</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>26.17</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BG120" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr"/>
@@ -34019,47 +34019,47 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>686452</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Drew Millas</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-06T23:45:00Z</t>
+          <t>2026-07-06T22:45:00Z</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Mike Burrows</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>681347</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -34068,7 +34068,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -34086,22 +34086,22 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>11.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q121" t="n">
-        <v>42.9</v>
+        <v>43.7</v>
       </c>
       <c r="R121" t="n">
-        <v>41.1</v>
+        <v>61.2</v>
       </c>
       <c r="S121" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T121" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U121" t="n">
-        <v>16.6</v>
+        <v>7</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -34158,7 +34158,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -34168,12 +34168,12 @@
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.1% barrel, 17.2 HR allowed</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -34183,112 +34183,112 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>96.8572</t>
+          <t>94.7821</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>0.3008</t>
+          <t>0.3044</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0786</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2784</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>69.94</t>
+          <t>67.68</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>18.47</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>0.1028</t>
+          <t>0.0989</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>38.99</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>88.36</t>
         </is>
       </c>
       <c r="BD121" t="inlineStr">
         <is>
-          <t>0.4006</t>
+          <t>0.4292</t>
         </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
-          <t>0.1525</t>
+          <t>0.1738</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>27.68</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr"/>
@@ -36330,7 +36330,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -36354,7 +36354,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>94.7</v>
+        <v>99.5</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -36610,7 +36610,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -37450,7 +37450,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -38010,7 +38010,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Player challenge</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -38850,7 +38850,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -41341,47 +41341,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-06T22:45:00Z</t>
+          <t>2026-07-07T01:40:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Miles Mikolas</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>571945</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -41390,7 +41390,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -41408,22 +41408,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>44.4</v>
+        <v>50.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>57.9</v>
+        <v>56.1</v>
       </c>
       <c r="R20" t="n">
-        <v>61.2</v>
+        <v>46.1</v>
       </c>
       <c r="S20" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>44.8</v>
+        <v>62.2</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -41475,12 +41475,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -41495,122 +41495,122 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 21.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>52.57</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>92.25</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.7846</t>
+          <t>104.1997</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4495</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1764</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3056</t>
+          <t>0.3574</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>75.19</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.1248</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>41.04</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>89.89</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4899</t>
+          <t>0.4632</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.2172</t>
+          <t>0.2044</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -41621,27 +41621,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-07T01:40:00Z</t>
+          <t>2026-07-07T02:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -41651,22 +41651,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -41684,26 +41684,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>50.2</v>
+        <v>45.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>56.1</v>
+        <v>59.9</v>
       </c>
       <c r="R21" t="n">
-        <v>46.1</v>
+        <v>62.6</v>
       </c>
       <c r="S21" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T21" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>62.2</v>
+        <v>19.9</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -41755,142 +41755,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/23, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.5% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.2% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>52.57</t>
+          <t>45.89</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>92.25</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>104.1997</t>
+          <t>101.01</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4495</t>
+          <t>0.4361</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.1871</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3574</t>
+          <t>0.3286</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>75.19</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>25.12</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>33.94</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1248</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>44.71</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.89</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4632</t>
+          <t>0.4856</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.2044</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
